--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,14 +875,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45163.60867533483</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45238</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="19">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -962,7 +957,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>118.259</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="19" thickBot="1">
@@ -980,7 +975,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>165.114</v>
+        <v>192.5</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="19">
@@ -1013,20 +1008,6 @@
       <c r="E21" s="6" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="34.5" customHeight="1" s="19" thickBot="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
@@ -1071,7 +1052,7 @@
         <v>100</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>208.303</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" ht="23.25" customHeight="1" s="19" thickBot="1">
@@ -1089,19 +1070,9 @@
         <v>50</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>222.928</v>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
+        <v>248</v>
+      </c>
+    </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
@@ -1111,11 +1082,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="19">

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45239</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="19">
@@ -1082,11 +1082,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="19">
@@ -1082,11 +1082,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="19">

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="19">

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,9 +875,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45254.59210599807</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1" s="19">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -957,7 +962,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>125.5</v>
+        <v>161.51</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="19" thickBot="1">
@@ -975,7 +980,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>192.5</v>
+        <v>247.74</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="19">
@@ -1008,6 +1013,20 @@
       <c r="E21" s="6" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36" ht="34.5" customHeight="1" s="19" thickBot="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
@@ -1052,7 +1071,7 @@
         <v>100</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>231</v>
+        <v>297.29</v>
       </c>
     </row>
     <row r="39" ht="23.25" customHeight="1" s="19" thickBot="1">
@@ -1070,9 +1089,19 @@
         <v>50</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>248</v>
-      </c>
-    </row>
+        <v>319.17</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
@@ -1082,11 +1111,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
+++ b/LISTAS/ma/ESCUADRA para ALACENA DISMAY.xlsx
@@ -875,14 +875,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45254.59210599807</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="19">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -962,7 +957,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>161.51</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="19" thickBot="1">
@@ -980,7 +975,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>247.74</v>
+        <v>192.5</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="19">
@@ -1013,20 +1008,6 @@
       <c r="E21" s="6" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="34.5" customHeight="1" s="19" thickBot="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
@@ -1071,7 +1052,7 @@
         <v>100</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>297.29</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" ht="23.25" customHeight="1" s="19" thickBot="1">
@@ -1089,19 +1070,9 @@
         <v>50</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>319.17</v>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
+        <v>248</v>
+      </c>
+    </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
@@ -1111,8 +1082,8 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A12:E12"/>
